--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,7 +611,7 @@
           <t>Nexoes</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Loveseat</t>
         </is>
@@ -624,11 +624,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-Make the room feel complete with JAMBI Loveseat and its Transitional character. Built as a nexoes loveseat, it pairs well with a wide range of interiors. Finished in Brown tones, the Breathable Leather, Solid Wood, Others build balances durability with visual appeal.
-Product Dimensions: 77" W x 41.3"D x 41.1" H
+Make the room feel complete with JAMBI Loveseat and its Transitional character. Built as a nexoes loveseat, it pairs well with a wide range of interiors. Finished in Brown tones, the Breathable Leather, Solid Wood, build balances durability with visual appeal.
+Product Dimensions: 77"W X 41.3"D X 41.1"H
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Breathable Leather, Solid Wood, Others
+Materials: Breathable Leather, Solid Wood.
 Color: Brown
 Weight: 99 lbs</t>
         </is>
@@ -729,7 +729,7 @@
           <t>Nexoes</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
@@ -742,11 +742,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-JAMBI Rocker Recliner brings a Transitional look to your home with a refined, comfortable feel. As a nexoes chair, it is designed to complement your space. The Breathable Leather, Solid Wood, Others construction is complemented by Brown tones for a polished look.
-Product Dimensions: 45.9" W x 41.3"D x 41.1" H
+JAMBI Rocker Recliner brings a Transitional look to your home with a refined, comfortable feel. As a nexoes chair, it is designed to complement your space. The Breathable Leather, Solid Wood, construction is complemented by Brown tones for a polished look.
+Product Dimensions: 45.9"W X 41.3"D X 41.1"H
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Breathable Leather, Solid Wood, Others
+Materials: Breathable Leather, Solid Wood.
 Color: Brown
 Weight: 55.5 lbs</t>
         </is>
@@ -847,7 +847,7 @@
           <t>Nexoes</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Sofa</t>
         </is>
@@ -860,11 +860,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-Elevate your space with JAMBI Sofa, styled in Transitional and designed for everyday comfort. This nexoes sofa is made to fit naturally into the room. With Breathable Leather, Solid Wood, Others and Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: 87.4" W x 41.3"D x 41.1" H
+Elevate your space with JAMBI Sofa, styled in Transitional and designed for everyday comfort. This nexoes sofa is made to fit naturally into the room. With Breathable Leather, Solid Wood, and Brown tones, it blends structure and softness in one clean profile.
+Product Dimensions: 87.4"W X 41.3"D X 41.1"H
 Features
 - Made with solid wood &amp; wood veneer
-Materials: Breathable Leather, Solid Wood, Others
+Materials: Breathable Leather, Solid Wood.
 Color: Brown
 Weight: 108 lbs</t>
         </is>

--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,183 +445,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>seo title(70char)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>seo title(70char)</t>
+          <t>seo description(160char)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>seo description(160char)</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Short Description - Red Text</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Short Description - Red Text</t>
+          <t>Item Type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Parts for Group Items</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Parts for Group Items</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>East(cost)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>East(cost)</t>
+          <t>EAST COST (Updated)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>EAST COST (Updated)</t>
+          <t>MSRP</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>MSRP</t>
+          <t>Weight (LB)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Weight (LB)</t>
+          <t>Product Dimension (Inch)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Product Dimension (Inch)</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Shipping Length (IN)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Shipping Length (IN)</t>
+          <t>Shipping Width (IN)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Shipping Width (IN)</t>
+          <t>Shipping Height (IN)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Shipping Height (IN)</t>
+          <t>Volume (CUFT)</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Volume (CUFT)</t>
+          <t>Fixed tags</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Variable tags</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Brown</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NX6011BR-LV</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NX6011BR-LV</t>
+          <t>Nexoes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nexoes</t>
+          <t>Loveseat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Loveseat</t>
+          <t>JAMBI Loveseat</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>JAMBI Loveseat</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Make the room feel complete with JAMBI Loveseat and its Transitional character. Built as a nexoes loveseat, it pairs well with a wide range of interiors. Finished in Brown tones, the Breathable Leather, Solid Wood, build balances durability with visual appeal.
@@ -633,113 +638,123 @@
 Weight: 99 lbs</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>JAMBI Loveseat in Brown | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JAMBI Loveseat in Brown | GOODDEGG</t>
+          <t>The JAMBI Loveseat offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>The JAMBI Loveseat offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMBI</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>JAMBI</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>Loveseat</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>NX6011BR-LV-1.jpg,NX6011BR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="P2" t="n">
         <v>510</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="Q2" s="1" t="n">
         <v>510</v>
       </c>
+      <c r="R2" t="n">
+        <v>1080</v>
+      </c>
       <c r="S2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="T2" t="n">
         <v>99</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>77"W X 41.3"D X 41.1"H</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>77"W X 41.3"D X 41.1"H</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Breathable Leather, Solid Wood, Others</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Breathable Leather, Solid Wood, Others</t>
+          <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Console with Metal Cup Holders on Loveseat</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Console with Metal Cup Holders on Loveseat</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y2" t="n">
+        <v>77.8</v>
+      </c>
       <c r="Z2" t="n">
-        <v>77.8</v>
+        <v>31.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>31.1</v>
+        <v>29.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="AC2" t="n">
         <v>41.9</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Nexoes, Loveseat, JAMBI</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Brown</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NX6011BR-CH</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NX6011BR-CH</t>
+          <t>Nexoes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nexoes</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>JAMBI Rocker Recliner</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>JAMBI Rocker Recliner</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 JAMBI Rocker Recliner brings a Transitional look to your home with a refined, comfortable feel. As a nexoes chair, it is designed to complement your space. The Breathable Leather, Solid Wood, construction is complemented by Brown tones for a polished look.
@@ -751,113 +766,123 @@
 Weight: 55.5 lbs</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>JAMBI Rocker Recliner in Brown | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JAMBI Rocker Recliner in Brown | GOODDEGG</t>
+          <t>The JAMBI Rocker Recliner adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The JAMBI Rocker Recliner adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMBI</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>JAMBI</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>Rocker Recliner</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>NX6011BR-CH-1.jpg,NX6011BR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="P3" t="n">
         <v>310</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="Q3" s="1" t="n">
         <v>310</v>
       </c>
+      <c r="R3" t="n">
+        <v>630</v>
+      </c>
       <c r="S3" t="n">
-        <v>630</v>
-      </c>
-      <c r="T3" t="n">
         <v>55.5</v>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>45.9"W X 41.3"D X 41.1"H</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.9"W X 41.3"D X 41.1"H</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Breathable Leather, Solid Wood, Others</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Breathable Leather, Solid Wood, Others</t>
+          <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Drop-down Table on Sofa with Metal Cup Holders</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Drop-down Table on Sofa with Metal Cup Holders</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y3" t="n">
+        <v>30.8</v>
+      </c>
       <c r="Z3" t="n">
-        <v>30.8</v>
+        <v>46.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.1</v>
+        <v>29.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="AC3" t="n">
         <v>24.4</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Nexoes, Chair, JAMBI</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Brown</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NX6011BR-SF</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NX6011BR-SF</t>
+          <t>Nexoes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nexoes</t>
+          <t>Sofa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sofa</t>
+          <t>JAMBI Sofa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>JAMBI Sofa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Elevate your space with JAMBI Sofa, styled in Transitional and designed for everyday comfort. This nexoes sofa is made to fit naturally into the room. With Breathable Leather, Solid Wood, and Brown tones, it blends structure and softness in one clean profile.
@@ -869,84 +894,94 @@
 Weight: 108 lbs</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>JAMBI Sofa in Brown | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JAMBI Sofa in Brown | GOODDEGG</t>
+          <t>The JAMBI Sofa offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>The JAMBI Sofa offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMBI</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>JAMBI</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>Sofa</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>NX6011BR-SF-1.jpg,NX6011BR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="P4" t="n">
         <v>549</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>549</v>
       </c>
+      <c r="R4" t="n">
+        <v>1137</v>
+      </c>
       <c r="S4" t="n">
-        <v>1137</v>
-      </c>
-      <c r="T4" t="n">
         <v>108</v>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>87.4"W X 41.3"D X 41.1"H</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>87.4"W X 41.3"D X 41.1"H</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Breathable Leather, Solid Wood, Others</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Breathable Leather, Solid Wood, Others</t>
+          <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Drop-down Table on Sofa with Metal Cup Holders</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Drop-down Table on Sofa with Metal Cup Holders</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y4" t="n">
+        <v>88</v>
+      </c>
       <c r="Z4" t="n">
-        <v>88</v>
+        <v>31.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>31.1</v>
+        <v>29.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="AC4" t="n">
         <v>47.4</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Nexoes, Sofa, JAMBI</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -628,14 +628,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with JAMBI Loveseat and its Transitional character. Built as a nexoes loveseat, it pairs well with a wide range of interiors. Finished in Brown tones, the Breathable Leather, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 77"W X 41.3"D X 41.1"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Breathable Leather, Solid Wood.
-Color: Brown
-Weight: 99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with JAMBI Loveseat and its Transitional character. Built as a nexoes loveseat, it pairs well with a wide range of interiors. Finished in Brown tones, the Breathable Leather, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 77"W X 41.3"D X 41.1"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leather, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JAMBI Rocker Recliner brings a Transitional look to your home with a refined, comfortable feel. As a nexoes chair, it is designed to complement your space. The Breathable Leather, Solid Wood, construction is complemented by Brown tones for a polished look.
-Product Dimensions: 45.9"W X 41.3"D X 41.1"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Breathable Leather, Solid Wood.
-Color: Brown
-Weight: 55.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JAMBI Rocker Recliner brings a Transitional look to your home with a refined, comfortable feel. As a nexoes chair, it is designed to complement your space. The Breathable Leather, Solid Wood, construction is complemented by Brown tones for a polished look.&lt;br&gt;
+Product Dimensions: 45.9"W X 41.3"D X 41.1"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leather, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 55.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -884,14 +884,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with JAMBI Sofa, styled in Transitional and designed for everyday comfort. This nexoes sofa is made to fit naturally into the room. With Breathable Leather, Solid Wood, and Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: 87.4"W X 41.3"D X 41.1"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Breathable Leather, Solid Wood.
-Color: Brown
-Weight: 108 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with JAMBI Sofa, styled in Transitional and designed for everyday comfort. This nexoes sofa is made to fit naturally into the room. With Breathable Leather, Solid Wood, and Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 87.4"W X 41.3"D X 41.1"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leather, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 108 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +597,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -724,7 +739,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Nexoes, Loveseat, JAMBI</t>
+          <t>Nexoes, Loveseat, JAMBI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas &gt; Loveseat Sofas</t>
         </is>
       </c>
     </row>
@@ -852,7 +882,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Nexoes, Chair, JAMBI</t>
+          <t>Nexoes, Chair, JAMBI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -980,7 +1025,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Nexoes, Sofa, JAMBI</t>
+          <t>Nexoes, Sofa, JAMBI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>

--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">

--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JAMBI Loveseat in Brown | GOODDEGG</t>
+          <t>JAMBI Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The JAMBI Loveseat offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMBI Loveseat supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>JAMBI Rocker Recliner in Brown | GOODDEGG</t>
+          <t>JAMBI Rocker Recliner | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The JAMBI Rocker Recliner adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMBI Rocker Recliner Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>JAMBI Sofa in Brown | GOODDEGG</t>
+          <t>JAMBI Sofa | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The JAMBI Sofa offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMBI Sofa supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/Nexoes-Single.xlsx
+++ b/FOA Singles/Nexoes-Single.xlsx
@@ -445,171 +445,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seo title(70char)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>seo description(160char)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Short Description - Red Text</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Item Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Parts for Group Items</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Images</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Image src</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>combine image src</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>East(cost)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>EAST COST (Updated)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MSRP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Weight (LB)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Dimension (Inch)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Shipping Length (IN)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Shipping Width (IN)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Shipping Height (IN)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Volume (CUFT)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Fixed tags</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Variable tags</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
@@ -618,30 +633,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>jambi-loveseat</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Brown</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>NX6011BR-LV</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Nexoes</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Loveseat</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>JAMBI Loveseat</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with JAMBI Loveseat and its Transitional character. Built as a nexoes loveseat, it pairs well with a wide range of interiors. Finished in Brown tones, the Breathable Leather, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
@@ -653,106 +673,112 @@
 Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>JAMBI Loveseat | GOODDEGG</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>JAMBI Loveseat supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>JAMBI</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Loveseat</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>NX6011BR-LV-1.jpg,NX6011BR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>NX6011BR-LV-1.jpg,NX6011BR-1-Z.jpg</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>510</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="T2" s="1" t="n">
         <v>510</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>1080</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>99</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>77"W X 41.3"D X 41.1"H</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Breathable Leather, Solid Wood, Others</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Console with Metal Cup Holders on Loveseat</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>77.8</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>31.1</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>29.9</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>41.9</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Nexoes, Loveseat, JAMBI, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas &gt; Loveseat Sofas</t>
         </is>
@@ -761,30 +787,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>jambi-rocker-recliner</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Brown</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>NX6011BR-CH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Nexoes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>JAMBI Rocker Recliner</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 JAMBI Rocker Recliner brings a Transitional look to your home with a refined, comfortable feel. As a nexoes chair, it is designed to complement your space. The Breathable Leather, Solid Wood, construction is complemented by Brown tones for a polished look.&lt;br&gt;
@@ -796,106 +827,112 @@
 Weight: 55.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>JAMBI Rocker Recliner | GOODDEGG</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>JAMBI Rocker Recliner Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>JAMBI</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Rocker Recliner</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>NX6011BR-CH-1.jpg,NX6011BR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>NX6011BR-CH-1.jpg,NX6011BR-1-Z.jpg</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>310</v>
       </c>
-      <c r="Q3" s="1" t="n">
+      <c r="T3" s="1" t="n">
         <v>310</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>630</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>55.5</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>45.9"W X 41.3"D X 41.1"H</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Breathable Leather, Solid Wood, Others</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Drop-down Table on Sofa with Metal Cup Holders</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>30.8</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>46.1</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>29.8</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>24.4</v>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Nexoes, Chair, JAMBI, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Furniture &gt; Chairs</t>
         </is>
@@ -904,30 +941,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>jambi-sofa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Brown</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>NX6011BR-SF</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Nexoes</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Sofa</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>JAMBI Sofa</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with JAMBI Sofa, styled in Transitional and designed for everyday comfort. This nexoes sofa is made to fit naturally into the room. With Breathable Leather, Solid Wood, and Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
@@ -939,106 +981,112 @@
 Weight: 108 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>JAMBI Sofa | GOODDEGG</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>JAMBI Sofa supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>JAMBI</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Sofa</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>NX6011BR-SF-1.jpg,NX6011BR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>NX6011BR-SF-1.jpg,NX6011BR-1-Z.jpg</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>549</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="T4" s="1" t="n">
         <v>549</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>1137</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>108</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>87.4"W X 41.3"D X 41.1"H</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Breathable Leather, Solid Wood, Others</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Transitional,Brown,Breathable Leather, Solid Wood, Others,Pillow Top Arms,Drop-down Table on Sofa with Metal Cup Holders</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>88</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>31.1</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
         <v>29.9</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>47.4</v>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Nexoes, Sofa, JAMBI, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
